--- a/delivery/paid-products/fazla-mesai-ve-isci-dava-riski-tespit-dosyasi/current.xlsx
+++ b/delivery/paid-products/fazla-mesai-ve-isci-dava-riski-tespit-dosyasi/current.xlsx
@@ -2347,6 +2347,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="A14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
@@ -2579,6 +2777,204 @@
       </mc:AlternateContent>
     </comment>
     <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2875,6 +3271,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="C14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="D6" authorId="0">
       <text>
         <r>
@@ -3139,6 +3733,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="D14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="E6" authorId="0">
       <text>
         <r>
@@ -3371,6 +4163,204 @@
       </mc:AlternateContent>
     </comment>
     <comment ref="E13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5459,6 +6449,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="A14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
@@ -5691,6 +6879,204 @@
       </mc:AlternateContent>
     </comment>
     <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5987,6 +7373,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="C14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="D6" authorId="0">
       <text>
         <r>
@@ -6219,6 +7803,204 @@
       </mc:AlternateContent>
     </comment>
     <comment ref="D13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer tüm hesaplamaları ve raporu doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>9</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -8421,7 +10203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="349">
   <si>
     <t xml:space="preserve">FAZLA MESAİ VE İŞÇİ DAVA RİSKİ TESPİT DOSYASI</t>
   </si>
@@ -8568,6 +10350,24 @@
   </si>
   <si>
     <t xml:space="preserve">Fatma Arslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İbrahim Korkmaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merve Çetin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Doğan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gülşah Öztürk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kemal Yavuz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selma Erdoğan</t>
   </si>
   <si>
     <t xml:space="preserve">Saatlik ücret, mesai ücreti, 270 saat aşımı ve risk tutarı formülle üretilir; sarı hücreler giriştir.</t>
@@ -10295,7 +12095,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>₺ 612.300</c:v>
+                  <c:v>₺ 1.143.000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10427,10 +12227,10 @@
                 <c:formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>137625</c:v>
+                  <c:v>300450</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>117106.557377049</c:v>
+                  <c:v>246241.15755627</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10542,7 +12342,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>₺ 867.032</c:v>
+                  <c:v>₺ 1.689.691</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10620,11 +12420,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="53941232"/>
-        <c:axId val="74330141"/>
+        <c:axId val="77849572"/>
+        <c:axId val="92353001"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="53941232"/>
+        <c:axId val="77849572"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10657,7 +12457,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74330141"/>
+        <c:crossAx val="92353001"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10665,7 +12465,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74330141"/>
+        <c:axId val="92353001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10708,7 +12508,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53941232"/>
+        <c:crossAx val="77849572"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10816,7 +12616,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>22,88</c:v>
+                  <c:v>22,21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10886,7 +12686,7 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>160.5</c:v>
+                  <c:v>288.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10894,11 +12694,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="11327961"/>
-        <c:axId val="917812"/>
+        <c:axId val="94005788"/>
+        <c:axId val="18137161"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11327961"/>
+        <c:axId val="94005788"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10931,7 +12731,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="917812"/>
+        <c:crossAx val="18137161"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10939,7 +12739,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="917812"/>
+        <c:axId val="18137161"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10982,7 +12782,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11327961"/>
+        <c:crossAx val="94005788"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11090,7 +12890,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>₺ 4.335.158</c:v>
+                  <c:v>₺ 8.448.456</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11168,11 +12968,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="42990762"/>
-        <c:axId val="61686287"/>
+        <c:axId val="47368524"/>
+        <c:axId val="41698614"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42990762"/>
+        <c:axId val="47368524"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11205,7 +13005,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61686287"/>
+        <c:crossAx val="41698614"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11213,7 +13013,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61686287"/>
+        <c:axId val="41698614"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11256,7 +13056,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42990762"/>
+        <c:crossAx val="47368524"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11460,11 +13260,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="45941984"/>
-        <c:axId val="2616591"/>
+        <c:axId val="49352808"/>
+        <c:axId val="64973667"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45941984"/>
+        <c:axId val="49352808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11497,7 +13297,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2616591"/>
+        <c:crossAx val="64973667"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11505,7 +13305,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2616591"/>
+        <c:axId val="64973667"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11548,7 +13348,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45941984"/>
+        <c:crossAx val="49352808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11752,11 +13552,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17411966"/>
-        <c:axId val="17902003"/>
+        <c:axId val="70279969"/>
+        <c:axId val="80427940"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17411966"/>
+        <c:axId val="70279969"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11789,7 +13589,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17902003"/>
+        <c:crossAx val="80427940"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11797,7 +13597,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17902003"/>
+        <c:axId val="80427940"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11840,7 +13640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17411966"/>
+        <c:crossAx val="70279969"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13784,7 +15584,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -13818,7 +15618,7 @@
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="58" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -13833,7 +15633,7 @@
     </row>
     <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B6" s="59" t="str">
         <f aca="false">KararSonuc</f>
@@ -13842,7 +15642,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B7" s="60" t="str">
         <f aca="false">KararGerekce</f>
@@ -13852,84 +15652,84 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="32" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B10" s="35" t="n">
         <f aca="false">ToplamDavaRiskTutari</f>
-        <v>867031.557377049</v>
+        <v>1689691.15755627</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B11" s="35" t="n">
         <f aca="false">ToplamFazlaMesaiUcreti</f>
-        <v>612300</v>
+        <v>1143000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B12" s="35" t="n">
         <f aca="false">ToplamSinirAsimTutari</f>
-        <v>137625</v>
+        <v>300450</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B13" s="35" t="n">
         <f aca="false">KayitFarkiRiskTutari</f>
-        <v>117106.557377049</v>
+        <v>246241.15755627</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B14" s="36" t="n">
         <f aca="false">KayitFarkiOrani</f>
-        <v>0.191256830601093</v>
+        <v>0.215434083601286</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B15" s="34" t="n">
         <f aca="false">SinirAsimCalisan</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B16" s="36" t="n">
         <f aca="false">DavaRiskOrani</f>
-        <v>0.149633431085044</v>
+        <v>0.156661184210526</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B17" s="35" t="n">
         <f aca="false">ZamanaSimiPencereRiskTutari</f>
-        <v>4335157.78688525</v>
+        <v>8448455.78778135</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="40" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B18" s="34" t="n">
         <f aca="false">VeriKaliteSkoru</f>
@@ -13938,40 +15738,40 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13985,7 +15785,7 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="str">
         <f aca="false">IF(KayitFarkiOrani&gt;KayitFarkiEsik,"Belgesiz mesai yüksek; yazılı onay ve puantaj kaydı gerekli.","Kayıtlar yeterli.")</f>
-        <v>Kayıtlar yeterli.</v>
+        <v>Belgesiz mesai yüksek; yazılı onay ve puantaj kaydı gerekli.</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -14000,7 +15800,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="32" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14037,7 +15837,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="61" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -14110,7 +15910,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -14144,12 +15944,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="62" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14269,7 +16069,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -14303,32 +16103,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="63" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D6" s="45"/>
     </row>
@@ -14365,7 +16165,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -14399,47 +16199,47 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -14517,7 +16317,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -14551,7 +16351,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -14563,7 +16363,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -14575,866 +16375,866 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="65" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E6" s="67" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F6" s="67" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G6" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H6" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="65" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C7" s="69" t="n">
         <f aca="true">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E7" s="67" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F7" s="67" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G7" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H7" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C8" s="70" t="n">
         <v>1.5</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E8" s="67" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F8" s="67" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="G8" s="68" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H8" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C9" s="70" t="n">
         <v>1.25</v>
       </c>
       <c r="D9" s="65" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E9" s="67" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F9" s="67" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H9" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B10" s="65" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C10" s="70" t="n">
         <v>270</v>
       </c>
       <c r="D10" s="65" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="67" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="67" t="s">
         <v>254</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="G10" s="68" t="s">
         <v>255</v>
       </c>
-      <c r="F10" s="67" t="s">
-        <v>248</v>
-      </c>
-      <c r="G10" s="68" t="s">
-        <v>249</v>
-      </c>
       <c r="H10" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B11" s="65" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C11" s="70" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F11" s="67" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="G11" s="68" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="H11" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B12" s="65" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C12" s="70" t="n">
         <v>30</v>
       </c>
       <c r="D12" s="65" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E12" s="67" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F12" s="67" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G12" s="68" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="H12" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B13" s="65" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C13" s="70" t="n">
         <v>8</v>
       </c>
       <c r="D13" s="65" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E13" s="67" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="F13" s="67" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G13" s="68" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H13" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B14" s="65" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C14" s="71" t="n">
         <v>1E-007</v>
       </c>
       <c r="D14" s="65" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E14" s="67" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F14" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G14" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H14" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B15" s="65" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C15" s="70" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E15" s="67" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F15" s="67" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H15" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="65" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B16" s="65" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C16" s="72" t="n">
         <v>500000</v>
       </c>
       <c r="D16" s="65" t="s">
+        <v>282</v>
+      </c>
+      <c r="E16" s="67" t="s">
+        <v>283</v>
+      </c>
+      <c r="F16" s="67" t="s">
         <v>276</v>
       </c>
-      <c r="E16" s="67" t="s">
-        <v>277</v>
-      </c>
-      <c r="F16" s="67" t="s">
-        <v>270</v>
-      </c>
       <c r="G16" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H16" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="65" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B17" s="65" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C17" s="71" t="n">
         <v>0.15</v>
       </c>
       <c r="D17" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E17" s="67" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F17" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G17" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H17" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="65" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B18" s="65" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C18" s="71" t="n">
         <v>0.2</v>
       </c>
       <c r="D18" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E18" s="67" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F18" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G18" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H18" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="65" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B19" s="65" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C19" s="70" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E19" s="67" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F19" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G19" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H19" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="65" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B20" s="65" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C20" s="70" t="n">
         <v>90</v>
       </c>
       <c r="D20" s="65" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E20" s="67" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F20" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G20" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H20" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="65" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C21" s="70" t="n">
         <v>70</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E21" s="67" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F21" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G21" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H21" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="65" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B22" s="65" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C22" s="70" t="n">
         <v>10</v>
       </c>
       <c r="D22" s="65" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E22" s="67" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="F22" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G22" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H22" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="65" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B23" s="65" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C23" s="71" t="n">
         <v>0.1</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E23" s="67" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="F23" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G23" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H23" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="65" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B24" s="65" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C24" s="71" t="n">
         <v>0.1</v>
       </c>
       <c r="D24" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E24" s="67" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F24" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G24" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H24" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="65" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B25" s="65" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C25" s="71" t="n">
         <v>0.05</v>
       </c>
       <c r="D25" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E25" s="67" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F25" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G25" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H25" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="65" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B26" s="65" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C26" s="71" t="n">
         <v>0.3</v>
       </c>
       <c r="D26" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E26" s="67" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F26" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G26" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H26" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="65" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B27" s="65" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C27" s="71" t="n">
         <v>0.9</v>
       </c>
       <c r="D27" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E27" s="67" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F27" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G27" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H27" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="65" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B28" s="65" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C28" s="71" t="n">
         <v>0.1</v>
       </c>
       <c r="D28" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E28" s="67" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F28" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G28" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H28" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B29" s="65" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C29" s="70" t="n">
         <v>45</v>
       </c>
       <c r="D29" s="65" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E29" s="67" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F29" s="67" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G29" s="68" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="H29" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="65" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B30" s="65" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C30" s="70" t="n">
         <v>1800</v>
       </c>
       <c r="D30" s="65" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E30" s="67" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G30" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H30" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="65" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B31" s="65" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C31" s="70" t="n">
         <v>100</v>
       </c>
       <c r="D31" s="65" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E31" s="67" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="F31" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G31" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H31" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="65" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B32" s="65" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C32" s="70" t="n">
         <v>20</v>
       </c>
       <c r="D32" s="65" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E32" s="67" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F32" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G32" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H32" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="65" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B33" s="65" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C33" s="70" t="n">
         <v>3000</v>
       </c>
       <c r="D33" s="65" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E33" s="67" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F33" s="67" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="G33" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H33" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="65" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B34" s="65" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C34" s="71" t="n">
         <v>0.6</v>
       </c>
       <c r="D34" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E34" s="67" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="F34" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G34" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H34" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="65" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B35" s="65" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C35" s="71" t="n">
         <v>0.1</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E35" s="67" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="F35" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G35" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H35" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="65" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B36" s="65" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C36" s="71" t="n">
         <v>0.5</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E36" s="67" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F36" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G36" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H36" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="65" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B37" s="65" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C37" s="71" t="n">
         <v>0.5</v>
       </c>
       <c r="D37" s="65" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E37" s="67" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F37" s="67" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G37" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H37" s="68" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -15508,7 +17308,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -15542,12 +17342,12 @@
     </row>
     <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -15611,7 +17411,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -15675,7 +17475,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -15739,7 +17539,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -15803,7 +17603,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -15867,7 +17667,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -15931,7 +17731,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -15995,7 +17795,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -16059,7 +17859,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -16123,7 +17923,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -16187,7 +17987,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -16251,7 +18051,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -17143,7 +18943,7 @@
       </c>
       <c r="N6" s="21" t="n">
         <f aca="false">IF(OR($B6=""),"",IFERROR(MAX(0,DATEDIF($B6,raporTarihi,"D")),0))</f>
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17196,7 +18996,7 @@
       </c>
       <c r="N7" s="21" t="n">
         <f aca="false">IF(OR($B7=""),"",IFERROR(MAX(0,DATEDIF($B7,raporTarihi,"D")),0))</f>
-        <v>4087</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17249,7 +19049,7 @@
       </c>
       <c r="N8" s="21" t="n">
         <f aca="false">IF(OR($B8=""),"",IFERROR(MAX(0,DATEDIF($B8,raporTarihi,"D")),0))</f>
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17302,7 +19102,7 @@
       </c>
       <c r="N9" s="21" t="n">
         <f aca="false">IF(OR($B9=""),"",IFERROR(MAX(0,DATEDIF($B9,raporTarihi,"D")),0))</f>
-        <v>3052</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17355,7 +19155,7 @@
       </c>
       <c r="N10" s="21" t="n">
         <f aca="false">IF(OR($B10=""),"",IFERROR(MAX(0,DATEDIF($B10,raporTarihi,"D")),0))</f>
-        <v>6033</v>
+        <v>6034</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17408,7 +19208,7 @@
       </c>
       <c r="N11" s="21" t="n">
         <f aca="false">IF(OR($B11=""),"",IFERROR(MAX(0,DATEDIF($B11,raporTarihi,"D")),0))</f>
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17461,7 +19261,7 @@
       </c>
       <c r="N12" s="21" t="n">
         <f aca="false">IF(OR($B12=""),"",IFERROR(MAX(0,DATEDIF($B12,raporTarihi,"D")),0))</f>
-        <v>2596</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17514,104 +19314,326 @@
       </c>
       <c r="N13" s="21" t="n">
         <f aca="false">IF(OR($B13=""),"",IFERROR(MAX(0,DATEDIF($B13,raporTarihi,"D")),0))</f>
-        <v>3873</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="28"/>
+      <c r="A14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>41713</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>62000</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <f aca="false">IF(OR($A14="",$C14=""),"",IFERROR($C14/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>258.333333333333</v>
+      </c>
+      <c r="G14" s="20" t="n">
+        <f aca="false">IF(OR($F14="",$E14=""),"",IFERROR($F14*$E14*MesaiKatsayi,0))</f>
+        <v>8525</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <f aca="false">IF(OR($E14=""),"",IFERROR($E14*AySayisi,0))</f>
+        <v>264</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <f aca="false">IF(OR($H14=""),"",IFERROR(MAX(0,$H14-YillikMesaiSinir),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <f aca="false">IF(OR($I14="",$F14=""),"",IFERROR($I14*$F14*MesaiKatsayi,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <f aca="false">IF(OR($G14=""),"",IFERROR($G14/MAX(BolumPaydaTaban,$C14),0))</f>
+        <v>0.1375</v>
+      </c>
+      <c r="L14" s="22" t="n">
+        <f aca="false">IF(OR($A14=""),"",IFERROR(IF(COUNTIF(tblKayit[Çalışan Adı],$A14)=0,0,1-MIN(1,SUMIF(tblKayit[Çalışan Adı],$A14,tblKayit[Belgelenen Mesai Saati])/MAX(BolumPaydaTaban,SUMIF(tblKayit[Çalışan Adı],$A14,tblKayit[Bildirilen Mesai Saati])))),0))</f>
+        <v>0.272727272727273</v>
+      </c>
+      <c r="M14" s="20" t="n">
+        <f aca="false">IF(OR($G14="",$J14="",$L14=""),"",IFERROR($G14+$J14+$L14*($G14+$J14),0))</f>
+        <v>10850</v>
+      </c>
+      <c r="N14" s="21" t="n">
+        <f aca="false">IF(OR($B14=""),"",IFERROR(MAX(0,DATEDIF($B14,raporTarihi,"D")),0))</f>
+        <v>4531</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="28"/>
+      <c r="A15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>44958</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <f aca="false">IF(OR($A15="",$C15=""),"",IFERROR($C15/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>108.333333333333</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <f aca="false">IF(OR($F15="",$E15=""),"",IFERROR($F15*$E15*MesaiKatsayi,0))</f>
+        <v>812.5</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <f aca="false">IF(OR($E15=""),"",IFERROR($E15*AySayisi,0))</f>
+        <v>60</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <f aca="false">IF(OR($H15=""),"",IFERROR(MAX(0,$H15-YillikMesaiSinir),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <f aca="false">IF(OR($I15="",$F15=""),"",IFERROR($I15*$F15*MesaiKatsayi,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <f aca="false">IF(OR($G15=""),"",IFERROR($G15/MAX(BolumPaydaTaban,$C15),0))</f>
+        <v>0.03125</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <f aca="false">IF(OR($A15=""),"",IFERROR(IF(COUNTIF(tblKayit[Çalışan Adı],$A15)=0,0,1-MIN(1,SUMIF(tblKayit[Çalışan Adı],$A15,tblKayit[Belgelenen Mesai Saati])/MAX(BolumPaydaTaban,SUMIF(tblKayit[Çalışan Adı],$A15,tblKayit[Bildirilen Mesai Saati])))),0))</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="20" t="n">
+        <f aca="false">IF(OR($G15="",$J15="",$L15=""),"",IFERROR($G15+$J15+$L15*($G15+$J15),0))</f>
+        <v>812.5</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <f aca="false">IF(OR($B15=""),"",IFERROR(MAX(0,DATEDIF($B15,raporTarihi,"D")),0))</f>
+        <v>1286</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="28"/>
+      <c r="A16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>42865</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>52000</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>49</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="F16" s="20" t="n">
+        <f aca="false">IF(OR($A16="",$C16=""),"",IFERROR($C16/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>216.666666666667</v>
+      </c>
+      <c r="G16" s="20" t="n">
+        <f aca="false">IF(OR($F16="",$E16=""),"",IFERROR($F16*$E16*MesaiKatsayi,0))</f>
+        <v>12350</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <f aca="false">IF(OR($E16=""),"",IFERROR($E16*AySayisi,0))</f>
+        <v>456</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <f aca="false">IF(OR($H16=""),"",IFERROR(MAX(0,$H16-YillikMesaiSinir),0))</f>
+        <v>186</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <f aca="false">IF(OR($I16="",$F16=""),"",IFERROR($I16*$F16*MesaiKatsayi,0))</f>
+        <v>60450</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <f aca="false">IF(OR($G16=""),"",IFERROR($G16/MAX(BolumPaydaTaban,$C16),0))</f>
+        <v>0.2375</v>
+      </c>
+      <c r="L16" s="22" t="n">
+        <f aca="false">IF(OR($A16=""),"",IFERROR(IF(COUNTIF(tblKayit[Çalışan Adı],$A16)=0,0,1-MIN(1,SUMIF(tblKayit[Çalışan Adı],$A16,tblKayit[Belgelenen Mesai Saati])/MAX(BolumPaydaTaban,SUMIF(tblKayit[Çalışan Adı],$A16,tblKayit[Bildirilen Mesai Saati])))),0))</f>
+        <v>0.263157894736842</v>
+      </c>
+      <c r="M16" s="20" t="n">
+        <f aca="false">IF(OR($G16="",$J16="",$L16=""),"",IFERROR($G16+$J16+$L16*($G16+$J16),0))</f>
+        <v>91957.8947368421</v>
+      </c>
+      <c r="N16" s="21" t="n">
+        <f aca="false">IF(OR($B16=""),"",IFERROR(MAX(0,DATEDIF($B16,raporTarihi,"D")),0))</f>
+        <v>3379</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="28"/>
+      <c r="A17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>44044</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" s="20" t="n">
+        <f aca="false">IF(OR($A17="",$C17=""),"",IFERROR($C17/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>137.5</v>
+      </c>
+      <c r="G17" s="20" t="n">
+        <f aca="false">IF(OR($F17="",$E17=""),"",IFERROR($F17*$E17*MesaiKatsayi,0))</f>
+        <v>3712.5</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <f aca="false">IF(OR($E17=""),"",IFERROR($E17*AySayisi,0))</f>
+        <v>216</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <f aca="false">IF(OR($H17=""),"",IFERROR(MAX(0,$H17-YillikMesaiSinir),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <f aca="false">IF(OR($I17="",$F17=""),"",IFERROR($I17*$F17*MesaiKatsayi,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <f aca="false">IF(OR($G17=""),"",IFERROR($G17/MAX(BolumPaydaTaban,$C17),0))</f>
+        <v>0.1125</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <f aca="false">IF(OR($A17=""),"",IFERROR(IF(COUNTIF(tblKayit[Çalışan Adı],$A17)=0,0,1-MIN(1,SUMIF(tblKayit[Çalışan Adı],$A17,tblKayit[Belgelenen Mesai Saati])/MAX(BolumPaydaTaban,SUMIF(tblKayit[Çalışan Adı],$A17,tblKayit[Bildirilen Mesai Saati])))),0))</f>
+        <v>0.222222222222222</v>
+      </c>
+      <c r="M17" s="20" t="n">
+        <f aca="false">IF(OR($G17="",$J17="",$L17=""),"",IFERROR($G17+$J17+$L17*($G17+$J17),0))</f>
+        <v>4537.5</v>
+      </c>
+      <c r="N17" s="21" t="n">
+        <f aca="false">IF(OR($B17=""),"",IFERROR(MAX(0,DATEDIF($B17,raporTarihi,"D")),0))</f>
+        <v>2200</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="28"/>
+      <c r="A18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>41214</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="F18" s="20" t="n">
+        <f aca="false">IF(OR($A18="",$C18=""),"",IFERROR($C18/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>291.666666666667</v>
+      </c>
+      <c r="G18" s="20" t="n">
+        <f aca="false">IF(OR($F18="",$E18=""),"",IFERROR($F18*$E18*MesaiKatsayi,0))</f>
+        <v>18375</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <f aca="false">IF(OR($E18=""),"",IFERROR($E18*AySayisi,0))</f>
+        <v>504</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <f aca="false">IF(OR($H18=""),"",IFERROR(MAX(0,$H18-YillikMesaiSinir),0))</f>
+        <v>234</v>
+      </c>
+      <c r="J18" s="20" t="n">
+        <f aca="false">IF(OR($I18="",$F18=""),"",IFERROR($I18*$F18*MesaiKatsayi,0))</f>
+        <v>102375</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <f aca="false">IF(OR($G18=""),"",IFERROR($G18/MAX(BolumPaydaTaban,$C18),0))</f>
+        <v>0.2625</v>
+      </c>
+      <c r="L18" s="22" t="n">
+        <f aca="false">IF(OR($A18=""),"",IFERROR(IF(COUNTIF(tblKayit[Çalışan Adı],$A18)=0,0,1-MIN(1,SUMIF(tblKayit[Çalışan Adı],$A18,tblKayit[Belgelenen Mesai Saati])/MAX(BolumPaydaTaban,SUMIF(tblKayit[Çalışan Adı],$A18,tblKayit[Bildirilen Mesai Saati])))),0))</f>
+        <v>0.285714285714286</v>
+      </c>
+      <c r="M18" s="20" t="n">
+        <f aca="false">IF(OR($G18="",$J18="",$L18=""),"",IFERROR($G18+$J18+$L18*($G18+$J18),0))</f>
+        <v>155250</v>
+      </c>
+      <c r="N18" s="21" t="n">
+        <f aca="false">IF(OR($B18=""),"",IFERROR(MAX(0,DATEDIF($B18,raporTarihi,"D")),0))</f>
+        <v>5030</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="28"/>
+      <c r="A19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>45306</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <f aca="false">IF(OR($A19="",$C19=""),"",IFERROR($C19/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>100</v>
+      </c>
+      <c r="G19" s="20" t="n">
+        <f aca="false">IF(OR($F19="",$E19=""),"",IFERROR($F19*$E19*MesaiKatsayi,0))</f>
+        <v>450</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <f aca="false">IF(OR($E19=""),"",IFERROR($E19*AySayisi,0))</f>
+        <v>36</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <f aca="false">IF(OR($H19=""),"",IFERROR(MAX(0,$H19-YillikMesaiSinir),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <f aca="false">IF(OR($I19="",$F19=""),"",IFERROR($I19*$F19*MesaiKatsayi,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="22" t="n">
+        <f aca="false">IF(OR($G19=""),"",IFERROR($G19/MAX(BolumPaydaTaban,$C19),0))</f>
+        <v>0.01875</v>
+      </c>
+      <c r="L19" s="22" t="n">
+        <f aca="false">IF(OR($A19=""),"",IFERROR(IF(COUNTIF(tblKayit[Çalışan Adı],$A19)=0,0,1-MIN(1,SUMIF(tblKayit[Çalışan Adı],$A19,tblKayit[Belgelenen Mesai Saati])/MAX(BolumPaydaTaban,SUMIF(tblKayit[Çalışan Adı],$A19,tblKayit[Bildirilen Mesai Saati])))),0))</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="20" t="n">
+        <f aca="false">IF(OR($G19="",$J19="",$L19=""),"",IFERROR($G19+$J19+$L19*($G19+$J19),0))</f>
+        <v>450</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <f aca="false">IF(OR($B19=""),"",IFERROR(MAX(0,DATEDIF($B19,raporTarihi,"D")),0))</f>
+        <v>938</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23"/>
@@ -33366,7 +35388,7 @@
     </row>
     <row r="1006" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1006" s="11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B1006" s="11"/>
       <c r="C1006" s="11"/>
@@ -33507,7 +35529,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -33541,7 +35563,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -33551,7 +35573,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -33564,19 +35586,19 @@
         <v>27</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33584,7 +35606,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C6" s="19" t="n">
         <v>20</v>
@@ -33606,7 +35628,7 @@
         <v>42</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C7" s="19" t="n">
         <v>35</v>
@@ -33628,7 +35650,7 @@
         <v>43</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C8" s="19" t="n">
         <v>10</v>
@@ -33650,7 +35672,7 @@
         <v>44</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C9" s="19" t="n">
         <v>40</v>
@@ -33672,7 +35694,7 @@
         <v>45</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C10" s="19" t="n">
         <v>15</v>
@@ -33694,7 +35716,7 @@
         <v>46</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C11" s="19" t="n">
         <v>25</v>
@@ -33716,7 +35738,7 @@
         <v>47</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C12" s="19" t="n">
         <v>8</v>
@@ -33738,7 +35760,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C13" s="19" t="n">
         <v>30</v>
@@ -33756,52 +35778,136 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="29"/>
+      <c r="A14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <f aca="false">IF(OR($C14="",$D14=""),"",IFERROR($C14-$D14,0))</f>
+        <v>6</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <f aca="false">IF(OR($C14="",$D14=""),"",IFERROR(IF($C14=0,0,($C14-$D14)/$C14),0))</f>
+        <v>0.272727272727273</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="29"/>
+      <c r="A15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <f aca="false">IF(OR($C15="",$D15=""),"",IFERROR($C15-$D15,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <f aca="false">IF(OR($C15="",$D15=""),"",IFERROR(IF($C15=0,0,($C15-$D15)/$C15),0))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="29"/>
+      <c r="A16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <f aca="false">IF(OR($C16="",$D16=""),"",IFERROR($C16-$D16,0))</f>
+        <v>10</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <f aca="false">IF(OR($C16="",$D16=""),"",IFERROR(IF($C16=0,0,($C16-$D16)/$C16),0))</f>
+        <v>0.263157894736842</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="29"/>
+      <c r="A17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <f aca="false">IF(OR($C17="",$D17=""),"",IFERROR($C17-$D17,0))</f>
+        <v>4</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <f aca="false">IF(OR($C17="",$D17=""),"",IFERROR(IF($C17=0,0,($C17-$D17)/$C17),0))</f>
+        <v>0.222222222222222</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="29"/>
+      <c r="A18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <f aca="false">IF(OR($C18="",$D18=""),"",IFERROR($C18-$D18,0))</f>
+        <v>12</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <f aca="false">IF(OR($C18="",$D18=""),"",IFERROR(IF($C18=0,0,($C18-$D18)/$C18),0))</f>
+        <v>0.285714285714286</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="29"/>
+      <c r="A19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <f aca="false">IF(OR($C19="",$D19=""),"",IFERROR($C19-$D19,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <f aca="false">IF(OR($C19="",$D19=""),"",IFERROR(IF($C19=0,0,($C19-$D19)/$C19),0))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23"/>
@@ -49683,7 +51789,7 @@
     </row>
     <row r="2006" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2006" s="11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B2006" s="11"/>
       <c r="C2006" s="11"/>
@@ -49793,7 +51899,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -49827,26 +51933,26 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="32" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B7" s="34" t="n">
         <f aca="false">IFERROR(COUNT(tblCalisan[Çalışan Adı]),0)</f>
@@ -49855,124 +51961,124 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B8" s="34" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Aylık Fazla Mesai Saati]),0)</f>
-        <v>183</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B9" s="34" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Yıllık Mesai Saati]),0)</f>
-        <v>2196</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B10" s="35" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Aylık Fazla Mesai Ücreti (₺)])*AySayisi,0)</f>
-        <v>612300</v>
+        <v>1143000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B11" s="35" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Sınır Aşım Tutarı (₺)]),0)</f>
-        <v>137625</v>
+        <v>300450</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B12" s="34" t="n">
         <f aca="false">IFERROR(COUNTIF(tblCalisan[Yıllık Mesai Saati],"&gt;"&amp;YillikMesaiSinir),0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B13" s="36" t="n">
         <f aca="false">IFERROR(IF(SUM(tblKayit[Bildirilen Mesai Saati])=0,0,1-MIN(1,SUM(tblKayit[Belgelenen Mesai Saati])/MAX(BolumPaydaTaban,SUM(tblKayit[Bildirilen Mesai Saati])))),0)</f>
-        <v>0.191256830601093</v>
+        <v>0.215434083601286</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B14" s="35" t="n">
         <f aca="false">IFERROR(ToplamFazlaMesaiUcreti*KayitFarkiOrani,0)</f>
-        <v>117106.557377049</v>
+        <v>246241.15755627</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B15" s="34" t="n">
         <f aca="false">IFERROR(AVERAGE(tblCalisan[Aylık Fazla Mesai Saati]),0)</f>
-        <v>22.875</v>
+        <v>22.2142857142857</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B16" s="35" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Aylık Brüt Ücret (₺)]),0)</f>
-        <v>341000</v>
+        <v>608000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B17" s="35" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Aylık Brüt Ücret (₺)])*AySayisi,0)</f>
-        <v>4092000</v>
+        <v>7296000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B18" s="36" t="n">
         <f aca="false">IFERROR(ToplamFazlaMesaiUcreti/MAX(BolumPaydaTaban,YillikBrutUcretYuku),0)</f>
-        <v>0.149633431085044</v>
+        <v>0.156661184210526</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B19" s="35" t="n">
         <f aca="false">IFERROR((ToplamFazlaMesaiUcreti+ToplamSinirAsimTutari+KayitFarkiRiskTutari)*ZamanAsimiYil,0)</f>
-        <v>4335157.78688525</v>
+        <v>8448455.78778135</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">IFERROR(COUNTIF(tblCalisan[Aylık Fazla Mesai Saati],"&gt;"&amp;IFERROR(AVERAGE(tblCalisan[Aylık Fazla Mesai Saati])+UcretAnomaliZEsik*IFERROR(stdev.p(tblCalisan[Aylık Fazla Mesai Saati]),0),0)),0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B21" s="36" t="n">
         <f aca="false">IFERROR(IF(COUNT(tblCalisan[Çalışan Adı])=0,0,AnomaliCalisanAdedi/COUNT(tblCalisan[Çalışan Adı])),0)</f>
@@ -49981,66 +52087,66 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B22" s="34" t="n">
         <f aca="false">IFERROR(AVERAGE(tblCalisan[Haftalık Çalışma Saati]),0)</f>
-        <v>46.375</v>
+        <v>46.2857142857143</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B25" s="34" t="n">
         <f aca="false">IFERROR(AVERAGE(tblCalisan[Dönem Günü]),0)</f>
-        <v>3182.875</v>
+        <v>3059.64285714286</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B26" s="34" t="n">
         <f aca="false">IFERROR(SLOPE(tblCalisan[Aylık Fazla Mesai Saati],tblCalisan[Dönem Günü]),0)</f>
-        <v>0.00128806355613597</v>
+        <v>0.00471145704386501</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="33" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B27" s="36" t="n">
         <f aca="false">IFERROR(IF(SUM(tblCalisan[Aylık Fazla Mesai Saati])=0,0,MAX(tblCalisan[Aylık Fazla Mesai Saati])/SUM(tblCalisan[Aylık Fazla Mesai Saati])),0)</f>
-        <v>0.218579234972678</v>
+        <v>0.135048231511254</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="33" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B28" s="34" t="n">
         <f aca="false">IFERROR(IF(SUM(tblKayit[Bildirilen Mesai Saati])=0,0,SUM(tblKayit[Bildirilen Mesai Saati])-SUM(tblKayit[Belgelenen Mesai Saati])),0)</f>
-        <v>35</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="33" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B29" s="36" t="n">
         <f aca="false">IFERROR(IF(SUM(tblCalisan[Aylık Fazla Mesai Saati])=0,0,SUM(tblCalisan[Aylık Fazla Mesai Saati])/MAX(BolumPaydaTaban,SUM(tblCalisan[Haftalık Çalışma Saati])*4)),0)</f>
-        <v>0.123315363881402</v>
+        <v>0.119984567901235</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="33" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B30" s="36" t="n">
         <f aca="false">IFERROR(IF(COUNT(tblCalisan[Çalışan Adı])=0,0,AnomaliCalisanAdedi/COUNT(tblCalisan[Çalışan Adı])),0)</f>
@@ -50049,43 +52155,43 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="33" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B31" s="35" t="n">
         <f aca="false">IFERROR(MAX(ABS(SenaryoRiskKotumser-SenaryoRiskIyimser),ABS(SenaryoRiskUcretKotumser-SenaryoRiskUcretIyimser)),0)</f>
-        <v>173406.31147541</v>
+        <v>337938.231511254</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B32" s="35" t="n">
         <f aca="false">IFERROR(SenaryoRiskKotumser-SenaryoRiskBaz,0)</f>
-        <v>-86703.155737705</v>
+        <v>-168969.115755627</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="33" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B33" s="35" t="n">
         <f aca="false">IFERROR(ZamanaSimiPencereRiskTutari,0)</f>
-        <v>4335157.78688525</v>
+        <v>8448455.78778135</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="33" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B34" s="34" t="n">
         <f aca="false">IFERROR(IF(SUM(tblCalisan[Aylık Fazla Mesai Saati])=0,0,SUMPRODUCT(tblCalisan[Aylık Fazla Mesai Saati],tblCalisan[Aylık Fazla Mesai Saati])/MAX(BolumPaydaTaban,SUM(tblCalisan[Aylık Fazla Mesai Saati])^2)),0)</f>
-        <v>0.153453372749261</v>
+        <v>0.0950052212032547</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="33" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B35" s="34" t="n">
         <f aca="false">VeriKaliteSkoru</f>
@@ -50094,7 +52200,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="33" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B36" s="34" t="n">
         <f aca="false">IFERROR(forecast.lınear(COUNT(tblKayit[Dönem])+1,tblCalisan[Aylık Fazla Mesai Saati],tblCalisan[Dönem Günü]),0)</f>
@@ -50103,7 +52209,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="33" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B37" s="35" t="n">
         <f aca="false">IFERROR(percentıle.ınc(tblCalisan[Risk Tutarı (₺)],P90Kuantil),0)</f>
@@ -50112,74 +52218,74 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="33" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B38" s="35" t="n">
         <f aca="false">IFERROR(NPV(IskontoOrani,ZamanaSimiPencereRiskTutari),0)</f>
-        <v>3941052.53353204</v>
+        <v>7680414.3525285</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="33" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B39" s="35" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamFazlaMesaiUcreti+ToplamSinirAsimTutari+KayitFarkiRiskTutari-DavaRiskButceEsik),0)</f>
-        <v>367031.557377049</v>
+        <v>1189691.15755627</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="33" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B40" s="35" t="n">
         <f aca="false">IFERROR(ToplamFazlaMesaiUcreti+ToplamSinirAsimTutari+KayitFarkiRiskTutari,0)</f>
-        <v>867031.557377049</v>
+        <v>1689691.15755627</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="33" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B41" s="35" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamDavaRiskTutari-DavaRiskButceEsik),0)</f>
-        <v>367031.557377049</v>
+        <v>1189691.15755627</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="33" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B42" s="36" t="n">
         <f aca="false">IFERROR(IF(MAX(BolumPaydaTaban,ToplamDavaRiskTutari)=0,0,MAX(0,ToplamDavaRiskTutari-DavaRiskButceEsik)/MAX(BolumPaydaTaban,ToplamDavaRiskTutari)),0)</f>
-        <v>0.423319721472879</v>
+        <v>0.704087934789735</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="37" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="33" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B45" s="34" t="n">
         <f aca="false">modulT1CalisanYasOrt</f>
-        <v>3182.875</v>
+        <v>3059.64285714286</v>
       </c>
       <c r="C45" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T1: Ortalama kıdem "&amp;modulT1CalisanYasOrt&amp;" gün",IF(modulT1CalisanYasOrt&gt;KidemSinirGun,"kıdem "&amp;KidemSinirGun/365&amp;" yıl üzerinde, zamanaşımı penceresi riski yüksek","kıdem pencere içinde"))</f>
-        <v>T1: Ortalama kıdem 3182,875 gün | kıdem 4,93150684931507 yıl üzerinde, zamanaşımı penceresi riski yüksek</v>
+        <v>T1: Ortalama kıdem 3059,64285714286 gün | kıdem 4,93150684931507 yıl üzerinde, zamanaşımı penceresi riski yüksek</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="33" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B46" s="34" t="n">
         <f aca="false">modulT2MesaiEgim</f>
-        <v>0.00128806355613597</v>
+        <v>0.00471145704386501</v>
       </c>
       <c r="C46" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T2: Mesai eğimi "&amp;TEXT(modulT2MesaiEgim,"0.0")&amp;" saat/gün",IF(modulT2MesaiEgim&gt;0,"mesai zamanla artıyor","mesai sabit veya azalıyor"))</f>
@@ -50188,37 +52294,37 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="33" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B47" s="36" t="n">
         <f aca="false">modulT3MesaiParetoPay</f>
-        <v>0.218579234972678</v>
+        <v>0.135048231511254</v>
       </c>
       <c r="C47" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T3: En yüksek mesaili çalışan toplamın %"&amp;TEXT(modulT3MesaiParetoPay*100,"0")&amp;"",IF(modulT3MesaiParetoPay&gt;ParetoEsikOran,"yoğunlaşma yüksek, tek çalışana bağımlılık var","dağılım dengeli"))</f>
-        <v>T3: En yüksek mesaili çalışan toplamın %22 | dağılım dengeli</v>
+        <v>T3: En yüksek mesaili çalışan toplamın %14 | dağılım dengeli</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="33" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B48" s="34" t="n">
         <f aca="false">modulT5KayitMutabakat</f>
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="C48" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T5: Bildirilen ile belgelenen fark "&amp;TEXT(modulT5KayitMutabakat,"#,##0")&amp;" saat",IF(modulT5KayitMutabakat&gt;0,"belgesiz mesai mevcut, dava riski artıyor","kayıtlar tutarlı"))</f>
-        <v>T5: Bildirilen ile belgelenen fark 35 saat | belgesiz mesai mevcut, dava riski artıyor</v>
+        <v>T5: Bildirilen ile belgelenen fark 67 saat | belgesiz mesai mevcut, dava riski artıyor</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="33" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B49" s="36" t="n">
         <f aca="false">modulT6NormalMesaiPay</f>
-        <v>0.123315363881402</v>
+        <v>0.119984567901235</v>
       </c>
       <c r="C49" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T6: Aylık mesai normal çalışmanın %"&amp;TEXT(modulT6NormalMesaiPay*100,"0")&amp;"",IF(modulT6NormalMesaiPay&gt;KayitFarkiEsik,"mesai yükü yüksek, "&amp;HaftalikCalismaSinir&amp;" saat üstü kontrol edilmeli","mesai yükü kabul edilebilir"))</f>
@@ -50227,7 +52333,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="33" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B50" s="36" t="n">
         <f aca="false">modulO1AnomaliOran</f>
@@ -50240,59 +52346,59 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="33" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B51" s="35" t="n">
         <f aca="false">modulO2TornadoZirve</f>
-        <v>173406.31147541</v>
+        <v>337938.231511254</v>
       </c>
       <c r="C51" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O2: Tornado zirve etki "&amp;TEXT(modulO2TornadoZirve,"#,##0")&amp;" ₺",IF(modulO2TornadoZirve&gt;DavaRiskButceEsik*ButceEtkiEsikOran,"risk duyarlılığı yüksek, mesai değişkeni kritik","duyarlılık düşük"))</f>
-        <v>O2: Tornado zirve etki 173.406 ₺ | risk duyarlılığı yüksek, mesai değişkeni kritik</v>
+        <v>O2: Tornado zirve etki 337.938 ₺ | risk duyarlılığı yüksek, mesai değişkeni kritik</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="33" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B52" s="35" t="n">
         <f aca="false">modulO3SenaryoBazFark</f>
-        <v>-86703.155737705</v>
+        <v>-168969.115755627</v>
       </c>
       <c r="C52" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O3: Kötümser-baz fark "&amp;TEXT(modulO3SenaryoBazFark,"#,##0")&amp;" ₺",IF(modulO3SenaryoBazFark&gt;DavaRiskButceEsik,"kötümser senaryoda bütçe aşılıyor","senaryo aralığı bütçe içinde"))</f>
-        <v>O3: Kötümser-baz fark -86.703 ₺ | senaryo aralığı bütçe içinde</v>
+        <v>O3: Kötümser-baz fark -168.969 ₺ | senaryo aralığı bütçe içinde</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="33" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B53" s="35" t="n">
         <f aca="false">modulO4ZamanAsimiRisk</f>
-        <v>4335157.78688525</v>
+        <v>8448455.78778135</v>
       </c>
       <c r="C53" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O4: "&amp;ZamanAsimiYil&amp;" yıllık pencere risk tutarı "&amp;TEXT(modulO4ZamanAsimiRisk,"#,##0")&amp;" ₺",IF(modulO4ZamanAsimiRisk&gt;DavaRiskButceEsik,"zamanaşımı penceresi riski bütçeyi aşıyor","pencere riski kabul edilebilir"))</f>
-        <v>O4: 5 yıllık pencere risk tutarı 4.335.158 ₺ | zamanaşımı penceresi riski bütçeyi aşıyor</v>
+        <v>O4: 5 yıllık pencere risk tutarı 8.448.456 ₺ | zamanaşımı penceresi riski bütçeyi aşıyor</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="33" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B54" s="34" t="n">
         <f aca="false">modulO6MesaiHhi</f>
-        <v>0.153453372749261</v>
+        <v>0.0950052212032547</v>
       </c>
       <c r="C54" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O6: Mesai yoğunlaşma endeksi "&amp;TEXT(modulO6MesaiHhi,"0.00")&amp;"",IF(modulO6MesaiHhi&gt;HhiYuksekEsik,"yoğunlaşma yüksek","dağılım dengeli"))</f>
-        <v>O6: Mesai yoğunlaşma endeksi 0,15 | dağılım dengeli</v>
+        <v>O6: Mesai yoğunlaşma endeksi 0,10 | dağılım dengeli</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="33" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B55" s="34" t="n">
         <f aca="false">modulO8KaliteSkoru</f>
@@ -50305,7 +52411,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="33" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B56" s="34" t="n">
         <f aca="false">modulI1MesaiTahminOrta</f>
@@ -50318,7 +52424,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="33" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B57" s="35" t="n">
         <f aca="false">modulI2RiskP90</f>
@@ -50331,33 +52437,33 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="33" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B58" s="35" t="n">
         <f aca="false">modulI3RiskNpv</f>
-        <v>3941052.53353204</v>
+        <v>7680414.3525285</v>
       </c>
       <c r="C58" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I3: Risk tutarının NPV değeri "&amp;TEXT(modulI3RiskNpv,"#,##0")&amp;" ₺",IF(modulI3RiskNpv&gt;DavaRiskButceEsik*NpvEsikOran,"NPV riski yüksek","NPV riski kabul edilebilir"))</f>
-        <v>I3: Risk tutarının NPV değeri 3.941.053 ₺ | NPV riski yüksek</v>
+        <v>I3: Risk tutarının NPV değeri 7.680.414 ₺ | NPV riski yüksek</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="33" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B59" s="35" t="n">
         <f aca="false">modulI7RiskAcikKopru</f>
-        <v>367031.557377049</v>
+        <v>1189691.15755627</v>
       </c>
       <c r="C59" s="38" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I7: Risk açık köprüsü "&amp;TEXT(modulI7RiskAcikKopru,"#,##0")&amp;" ₺",IF(modulI7RiskAcikKopru&gt;0,"risk bütçesi aşılıyor, kaynak planı gerekli","risk bütçesi içinde"))</f>
-        <v>I7: Risk açık köprüsü 367.032 ₺ | risk bütçesi aşılıyor, kaynak planı gerekli</v>
+        <v>I7: Risk açık köprüsü 1.189.691 ₺ | risk bütçesi aşılıyor, kaynak planı gerekli</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
@@ -50483,7 +52589,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -50517,14 +52623,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B5" s="39" t="n">
         <f aca="false">IFERROR(COUNT(tblCalisan[Çalışan Adı]),0)</f>
@@ -50533,7 +52639,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B6" s="39" t="n">
         <f aca="false">IFERROR(COUNT(tblKayit[Çalışan Adı]),0)</f>
@@ -50542,7 +52648,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B7" s="39" t="str">
         <f aca="false">IF(COUNTIF(tblCalisan[Aylık Brüt Ücret (₺)],"&lt;0")&gt;0,"FAIL","PASS")</f>
@@ -50551,7 +52657,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B8" s="39" t="str">
         <f aca="false">IF(COUNTIF(tblCalisan[Aylık Fazla Mesai Saati],"&lt;0")&gt;0,"FAIL","PASS")</f>
@@ -50560,7 +52666,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B9" s="39" t="str">
         <f aca="false">IF(COUNTIF(tblCalisan[Haftalık Çalışma Saati],"&gt;"&amp;HaftalikCalismaSinir)&gt;0,"WARN","PASS")</f>
@@ -50569,7 +52675,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B10" s="39" t="str">
         <f aca="false">IF(SUMPRODUCT(--(tblKayit[Belgelenen Mesai Saati]&gt;tblKayit[Bildirilen Mesai Saati]))&gt;0,"WARN","PASS")</f>
@@ -50578,7 +52684,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B11" s="39" t="str">
         <f aca="false">IF(COUNTIF(tblCalisan[Aylık Brüt Ücret (₺)],"")&gt;0,"FAIL","PASS")</f>
@@ -50587,7 +52693,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B12" s="39" t="str">
         <f aca="false">IF(COUNTIF(tblCalisan[İşe Giriş Tarihi],"")&gt;0,"WARN","PASS")</f>
@@ -50596,12 +52702,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B16" s="41" t="n">
         <f aca="false">COUNTIF(B5:B12,"PASS")</f>
@@ -50610,7 +52716,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B17" s="41" t="n">
         <f aca="false">COUNTIF(B5:B12,"FAIL")</f>
@@ -50619,7 +52725,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="40" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B18" s="41" t="n">
         <f aca="false">COUNTIF(B5:B12,"WARN")</f>
@@ -50628,7 +52734,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B19" s="34" t="n">
         <f aca="false">IFERROR(IF(DoluGirisHucre=0,0,MAX(0,VeriKaliteTaban-FAIL_Sayisi*VeriKaliteFailCeza-WARN_Sayisi*VeriKaliteUyariCeza)),0)</f>
@@ -50637,7 +52743,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="40" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B20" s="39" t="str">
         <f aca="false">IF(VeriKaliteSkoru&gt;=VeriKaliteIyiEsik,"İYİ",IF(VeriKaliteSkoru&gt;=VeriKaliteOrtaEsik,"ORTA","DÜŞÜK"))</f>
@@ -50646,7 +52752,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B21" s="41" t="n">
         <f aca="false">IFERROR(COUNT(tblCalisan[Çalışan Adı])+COUNT(tblKayit[Çalışan Adı]),0)</f>
@@ -50655,7 +52761,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="40" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B22" s="41" t="n">
         <f aca="false">IFERROR(ROWS(tblCalisan)+ROWS(tblKayit),0)</f>
@@ -50664,7 +52770,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="40" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B23" s="42" t="n">
         <f aca="false">IFERROR(DoluGirisHucre/KayitKapasite,0)</f>
@@ -50673,7 +52779,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="33" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B24" s="40" t="str">
         <f aca="false">IF(FAIL_Sayisi=0,"SAĞLIKLI","İNCELE")</f>
@@ -50682,7 +52788,7 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -50863,7 +52969,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -50897,53 +53003,53 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B6" s="35" t="n">
         <f aca="false">ToplamDavaRiskTutari</f>
-        <v>867031.557377049</v>
+        <v>1689691.15755627</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B7" s="35" t="n">
         <f aca="false">IFERROR(DavaRiskButceEsik-ToplamDavaRiskTutari,0)</f>
-        <v>-367031.557377049</v>
+        <v>-1189691.15755627</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B8" s="36" t="n">
         <f aca="false">DavaRiskOrani</f>
-        <v>0.149633431085044</v>
+        <v>0.156661184210526</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B9" s="34" t="n">
         <f aca="false">SinirAsimCalisan</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B11" s="43" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"VERİ YOK",IF(OR(ToplamDavaRiskTutari&lt;0,SinirAsimCalisan&lt;0),"DURDUR",IF(OR(KayitFarkiOrani&gt;KayitFarkiEsik,SinirAsimCalisan&gt;0),"DURDUR",IF(DavaRiskOrani&gt;DavaRiskEsik,"İNCELE",IF(AnomaliCalisanAdedi&gt;0,"İNCELE","UYGUN")))))</f>
@@ -50952,7 +53058,7 @@
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B12" s="44" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"Girdi eksik; lütfen sarı hücreleri doldurun.",IF(ToplamDavaRiskTutari&lt;0,"Risk tutarı negatif: ücret kayıtlarını kontrol edin.",IF(KayitFarkiOrani&gt;KayitFarkiEsik,"Kayıt farkı %"&amp;TEXT(KayitFarkiOrani,"0.0%")&amp;" eşik üstünde; belgesiz mesai dava riski yüksek.",IF(SinirAsimCalisan&gt;0,SinirAsimCalisan&amp;" çalışan 270 saat sınırını aşıyor; aşım tutarı "&amp;TEXT(ToplamSinirAsimTutari,"#,##0")&amp;" ₺.",IF(DavaRiskOrani&gt;DavaRiskEsik,"Dava risk oranı %"&amp;TEXT(DavaRiskOrani,"0.0%")&amp;" eşik üstünde; fazla mesai yükü yüksek.","Fazla mesai yükü ve kayıtlar eşikler içinde kabul edilebilir.")))))</f>
@@ -50961,7 +53067,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50991,14 +53097,14 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="str">
         <f aca="false">IF(RiskAcikKopru&gt;0,"Risk açığı "&amp;TEXT(RiskAcikKopru,"#,##0")&amp;" ₺; hukuk ve bütçe planını güçlendirin","Risk bütçesi içinde; planlama sürdürülebilir")</f>
-        <v>Risk açığı 367.032 ₺; hukuk ve bütçe planını güçlendirin</v>
+        <v>Risk açığı 1.189.691 ₺; hukuk ve bütçe planını güçlendirin</v>
       </c>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -51106,7 +53212,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -51140,41 +53246,41 @@
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="46" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="47" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B5" s="47"/>
       <c r="D5" s="48" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E5" s="48"/>
       <c r="G5" s="49" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H5" s="49"/>
       <c r="J5" s="50" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K5" s="50"/>
     </row>
     <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="n">
         <f aca="false">ToplamDavaRiskTutari</f>
-        <v>867031.557377049</v>
+        <v>1689691.15755627</v>
       </c>
       <c r="B6" s="51"/>
       <c r="D6" s="52" t="n">
         <f aca="false">KayitFarkiOrani</f>
-        <v>0.191256830601093</v>
+        <v>0.215434083601286</v>
       </c>
       <c r="E6" s="52"/>
       <c r="G6" s="53" t="n">
         <f aca="false">SinirAsimCalisan</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" s="53"/>
       <c r="J6" s="54" t="str">
@@ -51185,34 +53291,34 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="55" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B8" s="35" t="n">
         <f aca="false">ToplamFazlaMesaiUcreti</f>
-        <v>612300</v>
+        <v>1143000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="55" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B9" s="35" t="n">
         <f aca="false">ToplamSinirAsimTutari</f>
-        <v>137625</v>
+        <v>300450</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="55" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B10" s="35" t="n">
         <f aca="false">KayitFarkiRiskTutari</f>
-        <v>117106.557377049</v>
+        <v>246241.15755627</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="55" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B11" s="34" t="n">
         <f aca="false">ToplamCalisanSayisi</f>
@@ -51221,16 +53327,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="55" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B12" s="34" t="n">
         <f aca="false">AnomaliCalisanAdedi</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="55" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B13" s="34" t="n">
         <f aca="false">VeriKaliteSkoru</f>
@@ -51239,13 +53345,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="45" t="str">
         <f aca="false">"Toplam dava riski "&amp;TEXT(ToplamDavaRiskTutari,"#,##0")&amp;" ₺; kayıt farkı %"&amp;TEXT(KayitFarkiOrani,"0.0%")&amp;"."</f>
-        <v>Toplam dava riski 867.032 ₺; kayıt farkı %19%.</v>
+        <v>Toplam dava riski 1.689.691 ₺; kayıt farkı %22%.</v>
       </c>
       <c r="B16" s="45"/>
       <c r="C16" s="45"/>
@@ -51256,7 +53362,7 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="45" t="str">
         <f aca="false">"Fazla mesai ücreti "&amp;TEXT(ToplamFazlaMesaiUcreti,"#,##0")&amp;", sınır aşımı "&amp;TEXT(ToplamSinirAsimTutari,"#,##0")&amp;", kayıt farkı "&amp;TEXT(KayitFarkiRiskTutari,"#,##0")&amp;" ₺."</f>
-        <v>Fazla mesai ücreti 612.300, sınır aşımı 137.625, kayıt farkı 117.107 ₺.</v>
+        <v>Fazla mesai ücreti 1.143.000, sınır aşımı 300.450, kayıt farkı 246.241 ₺.</v>
       </c>
       <c r="B17" s="45"/>
       <c r="C17" s="45"/>
@@ -51267,7 +53373,7 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="str">
         <f aca="false">"Ortalama aylık mesai "&amp;TEXT(OrtalamaAylikMesaiSaati,"0.0")&amp;" saat; "&amp;AnomaliCalisanAdedi&amp;" çalışanda uç mesai var."</f>
-        <v>Ortalama aylık mesai 23 saat; 4 çalışanda uç mesai var.</v>
+        <v>Ortalama aylık mesai 22 saat; 6 çalışanda uç mesai var.</v>
       </c>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
@@ -51277,49 +53383,49 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="55" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C20" s="27" t="n">
         <f aca="false">ToplamFazlaMesaiUcreti</f>
-        <v>612300</v>
+        <v>1143000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C21" s="27" t="n">
         <f aca="false">ToplamSinirAsimTutari</f>
-        <v>137625</v>
+        <v>300450</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C22" s="27" t="n">
         <f aca="false">KayitFarkiRiskTutari</f>
-        <v>117106.557377049</v>
+        <v>246241.15755627</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="55" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C23" s="27" t="n">
         <f aca="false">ToplamDavaRiskTutari</f>
-        <v>867031.557377049</v>
+        <v>1689691.15755627</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C24" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,DavaRiskButceEsik-ToplamDavaRiskTutari),0)</f>
@@ -51328,40 +53434,40 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="55" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C26" s="31" t="n">
         <f aca="false">OrtalamaAylikMesaiSaati</f>
-        <v>22.875</v>
+        <v>22.2142857142857</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C27" s="31" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamYillikMesaiSaati/12-YillikMesaiSinir/12),0)</f>
-        <v>160.5</v>
+        <v>288.5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="55" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C29" s="27" t="n">
         <f aca="false">ZamanaSimiPencereRiskTutari</f>
-        <v>4335157.78688525</v>
+        <v>8448455.78778135</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C30" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,DavaRiskButceEsik-ZamanaSimiPencereRiskTutari),0)</f>
@@ -51370,12 +53476,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="32" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B33" s="56" t="str">
         <f aca="false">KararSonuc</f>
@@ -51387,7 +53493,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B34" s="57" t="str">
         <f aca="false">KararGerekce</f>
@@ -51399,7 +53505,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="55" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51454,7 +53560,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="55" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51509,7 +53615,7 @@
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -51633,7 +53739,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -51667,7 +53773,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -51677,26 +53783,26 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="32" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B7" s="36" t="n">
         <f aca="false">1-SenaryoKotumserKat*OrtalamaAylikMesaiSaati/MAX(OrtalamaAylikMesaiSaati,BolumPaydaTaban)</f>
@@ -51717,37 +53823,37 @@
       </c>
       <c r="B8" s="35" t="n">
         <f aca="false">IFERROR(ToplamDavaRiskTutari*(1-SenaryoKotumserKat*OrtalamaAylikMesaiSaati/MAX(OrtalamaAylikMesaiSaati,BolumPaydaTaban)),0)</f>
-        <v>780328.401639344</v>
+        <v>1520722.04180064</v>
       </c>
       <c r="C8" s="35" t="n">
         <f aca="false">ToplamDavaRiskTutari</f>
-        <v>867031.557377049</v>
+        <v>1689691.15755627</v>
       </c>
       <c r="D8" s="35" t="n">
         <f aca="false">IFERROR(ToplamDavaRiskTutari*(1+SenaryoIyimserKat*OrtalamaAylikMesaiSaati/MAX(OrtalamaAylikMesaiSaati,BolumPaydaTaban)),0)</f>
-        <v>953734.713114754</v>
+        <v>1858660.2733119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B9" s="36" t="n">
         <f aca="false">IFERROR(KayitFarkiOrani*(1+SenaryoKotumserKat*OrtalamaAylikMesaiSaati/MAX(OrtalamaAylikMesaiSaati,BolumPaydaTaban)),0)</f>
-        <v>0.210382513661202</v>
+        <v>0.236977491961415</v>
       </c>
       <c r="C9" s="36" t="n">
         <f aca="false">KayitFarkiOrani</f>
-        <v>0.191256830601093</v>
+        <v>0.215434083601286</v>
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">IFERROR(MAX(0,KayitFarkiOrani*(1-SenaryoIyimserKat*OrtalamaAylikMesaiSaati/MAX(OrtalamaAylikMesaiSaati,BolumPaydaTaban))),0)</f>
-        <v>0.172131147540984</v>
+        <v>0.193890675241158</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B10" s="39" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"VERİ YOK",IF(OR(B9&gt;KayitFarkiEsik,B8&gt;DavaRiskButceEsik),"DURDUR",IF(B8&gt;DavaRiskButceEsik*ButceInceleEsikOran,"İNCELE","UYGUN")))</f>
@@ -51764,114 +53870,114 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B13" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>178</v>
-      </c>
       <c r="D13" s="33" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B14" s="35" t="n">
         <f aca="false">ToplamDavaRiskTutari*(1-DuyarliDegisim)</f>
-        <v>823679.979508197</v>
+        <v>1605206.59967846</v>
       </c>
       <c r="C14" s="35" t="n">
         <f aca="false">ToplamDavaRiskTutari</f>
-        <v>867031.557377049</v>
+        <v>1689691.15755627</v>
       </c>
       <c r="D14" s="35" t="n">
         <f aca="false">ToplamDavaRiskTutari*(1+DuyarliDegisim)</f>
-        <v>910383.135245902</v>
+        <v>1774175.71543408</v>
       </c>
       <c r="E14" s="36" t="n">
         <f aca="false">B14/DavaRiskButceEsik</f>
-        <v>1.64735995901639</v>
+        <v>3.21041319935691</v>
       </c>
       <c r="F14" s="36" t="n">
         <f aca="false">D14/DavaRiskButceEsik</f>
-        <v>1.8207662704918</v>
+        <v>3.54835143086817</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B15" s="35" t="n">
         <f aca="false">ToplamDavaRiskTutari*(1-DuyarliDegisim)</f>
-        <v>823679.979508197</v>
+        <v>1605206.59967846</v>
       </c>
       <c r="C15" s="35" t="n">
         <f aca="false">ToplamDavaRiskTutari</f>
-        <v>867031.557377049</v>
+        <v>1689691.15755627</v>
       </c>
       <c r="D15" s="35" t="n">
         <f aca="false">ToplamDavaRiskTutari*(1+DuyarliDegisim)</f>
-        <v>910383.135245902</v>
+        <v>1774175.71543408</v>
       </c>
       <c r="E15" s="36" t="n">
         <f aca="false">B15/DavaRiskButceEsik</f>
-        <v>1.64735995901639</v>
+        <v>3.21041319935691</v>
       </c>
       <c r="F15" s="36" t="n">
         <f aca="false">D15/DavaRiskButceEsik</f>
-        <v>1.8207662704918</v>
+        <v>3.54835143086817</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="40" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B18" s="36" t="n">
         <f aca="false">IFERROR(DavaRiskOrani-DavaRiskEsik,0)</f>
-        <v>-0.000366568914956011</v>
+        <v>0.00666118421052633</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="40" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B19" s="36" t="n">
         <f aca="false">IFERROR(KayitFarkiOrani-KayitFarkiEsik,0)</f>
-        <v>-0.00874316939890713</v>
+        <v>0.0154340836012861</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="40" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamYillikMesaiSaati-YillikMesaiSinir*ToplamCalisanSayisi),0)</f>
-        <v>2196</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
